--- a/6.2 Geoffrey Bay/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/6.2 Geoffrey Bay/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.791108723173682</v>
+        <v>3.077779052813751</v>
       </c>
       <c r="C2" t="n">
-        <v>4.201880174176349</v>
+        <v>4.558254590817941</v>
       </c>
       <c r="D2" t="n">
-        <v>11.87914722138641</v>
+        <v>17.04314014572463</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.9443434804942</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="C3" t="n">
-        <v>9.851838212116743</v>
+        <v>11.10356653503143</v>
       </c>
       <c r="D3" t="n">
-        <v>44.92477494633405</v>
+        <v>59.47918466179301</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.83847895935156</v>
+        <v>35.4420738710141</v>
       </c>
       <c r="C4" t="n">
-        <v>36.68005772606933</v>
+        <v>39.75587328347459</v>
       </c>
       <c r="D4" t="n">
-        <v>54.58615410382691</v>
+        <v>68.9314515582813</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.9086660724386</v>
+        <v>46.51029748869265</v>
       </c>
       <c r="C5" t="n">
-        <v>64.47628047640929</v>
+        <v>64.81989217289566</v>
       </c>
       <c r="D5" t="n">
-        <v>40.22711218151306</v>
+        <v>47.00117134081605</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.45541742824607</v>
+        <v>35.26045054572845</v>
       </c>
       <c r="C6" t="n">
-        <v>67.78378849201678</v>
+        <v>68.06555008313562</v>
       </c>
       <c r="D6" t="n">
-        <v>31.11452999069417</v>
+        <v>32.20132469929539</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>22.0382724649324</v>
       </c>
       <c r="C7" t="n">
-        <v>54.5567016726995</v>
+        <v>53.41885608347744</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>28.56591295046944</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.46287049925253</v>
       </c>
       <c r="D8" t="n">
-        <v>25.78560345204247</v>
+        <v>26.03594911662541</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>19.96874830438012</v>
+        <v>19.74687332322034</v>
       </c>
       <c r="D9" t="n">
-        <v>23.74062298409636</v>
+        <v>23.85156047467625</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>15.9435827169682</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -906,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.132356013624072</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="C11" t="n">
         <v>14.21570675749381</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.518763698469816</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
         <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>22.34752299177014</v>
+        <v>23.43235420496287</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7804894248762143</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>18.99190933865455</v>
+        <v>21.33337761328319</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>10.14047203716531</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>16.59349969717959</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>8.958447801252145</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="D15" t="n">
-        <v>13.97517856995334</v>
+        <v>18.99190933865455</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>8.679631453246051</v>
       </c>
       <c r="D16" t="n">
-        <v>10.33289458719768</v>
+        <v>16.94594712300419</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>10.38885420633975</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>6.611089040398022</v>
+        <v>15.58328130950962</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>11.23610247510475</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>2.140209995258047</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>9.628981483252716</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>10.23079282595601</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4.707480241863455</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>41.97282370431214</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6.142364444533484</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.558655501445441</v>
+        <v>5.764822519337271</v>
       </c>
       <c r="C2" t="n">
-        <v>4.835107443415541</v>
+        <v>5.286711387369073</v>
       </c>
       <c r="D2" t="n">
-        <v>8.984954989266809</v>
+        <v>13.11124059021615</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.22628499806228</v>
+        <v>12.34056864238241</v>
       </c>
       <c r="C3" t="n">
-        <v>13.73955912093411</v>
+        <v>14.74585051778709</v>
       </c>
       <c r="D3" t="n">
-        <v>44.56643703428396</v>
+        <v>59.53318078552658</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.25215459573796</v>
+        <v>31.23037621979529</v>
       </c>
       <c r="C4" t="n">
-        <v>29.96686692442964</v>
+        <v>32.9022925601276</v>
       </c>
       <c r="D4" t="n">
-        <v>66.58311104972293</v>
+        <v>84.9359026329128</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.84823968313181</v>
+        <v>53.03891972193394</v>
       </c>
       <c r="C5" t="n">
-        <v>66.88156235181397</v>
+        <v>69.38501899764334</v>
       </c>
       <c r="D5" t="n">
-        <v>51.41903600992671</v>
+        <v>62.36552291227864</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.89067581859268</v>
+        <v>55.2655235151657</v>
       </c>
       <c r="C6" t="n">
-        <v>86.29955019411163</v>
+        <v>85.37376210900689</v>
       </c>
       <c r="D6" t="n">
-        <v>37.31328499530853</v>
+        <v>40.77492740048278</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.81219275551515</v>
+        <v>37.06981156465531</v>
       </c>
       <c r="C7" t="n">
-        <v>76.83452057746811</v>
+        <v>76.29554108783661</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.86075605691297</v>
+        <v>21.19593293468863</v>
       </c>
       <c r="C8" t="n">
-        <v>52.73948667213865</v>
+        <v>53.07328089158257</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>24.96093538047515</v>
+        <v>25.29374785221481</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>4.555309347705201</v>
       </c>
       <c r="C10" t="n">
-        <v>19.92947839621025</v>
+        <v>19.64477156197868</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.487748682561417</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
         <v>24.6997904911455</v>
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.735729941108361</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
         <v>14.53673825678252</v>
       </c>
       <c r="D12" t="n">
-        <v>22.99842171968578</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7804894248762143</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>18.99190933865455</v>
+        <v>22.11386703815941</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>9.316785713302231</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>13.25850274585317</v>
+        <v>19.35024725070463</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>16.94594712300419</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>10.38885420633975</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>15.58328130950962</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>11.77115497391926</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>1.605157496443535</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>9.027170140549421</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>10.23079282595601</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4.03498306445439</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>45.94691967136695</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7.309737220444743</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.049349427119598</v>
+        <v>8.289877614660067</v>
       </c>
       <c r="C2" t="n">
-        <v>3.399792299806704</v>
+        <v>3.787582642984194</v>
       </c>
       <c r="D2" t="n">
-        <v>13.90252923983908</v>
+        <v>20.70113209174824</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.60764507566654</v>
+        <v>17.78926840095221</v>
       </c>
       <c r="C3" t="n">
-        <v>16.44918278465531</v>
+        <v>17.64691498383642</v>
       </c>
       <c r="D3" t="n">
-        <v>41.77336481570178</v>
+        <v>56.20996480665113</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.38505038870978</v>
+        <v>27.28669569183585</v>
       </c>
       <c r="C4" t="n">
-        <v>32.55769911593697</v>
+        <v>34.51039529968388</v>
       </c>
       <c r="D4" t="n">
-        <v>74.0110141800543</v>
+        <v>94.9418752345963</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.96466674930968</v>
+        <v>51.19814277647117</v>
       </c>
       <c r="C5" t="n">
-        <v>61.04016351154545</v>
+        <v>64.37810570598461</v>
       </c>
       <c r="D5" t="n">
-        <v>64.30447462816609</v>
+        <v>79.84063204787186</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.72466264558373</v>
+        <v>67.66303352439442</v>
       </c>
       <c r="C6" t="n">
-        <v>97.04674231250146</v>
+        <v>97.61026549473914</v>
       </c>
       <c r="D6" t="n">
-        <v>44.84034464376883</v>
+        <v>50.99884799250906</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>54.61658828265855</v>
+        <v>57.43125895073415</v>
       </c>
       <c r="C7" t="n">
-        <v>100.2501850714588</v>
+        <v>98.333813552769</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.12769362147687</v>
+        <v>34.38080460272329</v>
       </c>
       <c r="C8" t="n">
-        <v>75.52094214918588</v>
+        <v>75.93818492349078</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.75312366234431</v>
+        <v>18.19374845510188</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>47.59218345877262</v>
       </c>
       <c r="D9" t="n">
-        <v>26.18124777685393</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -1528,7 +1528,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
         <v>19.19120412261664</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
         <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.30021917551705</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.040652566501619</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>18.73174619702914</v>
+        <v>22.89435646303562</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>10.0334615374024</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>19.70858516275472</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>9.092947236733956</v>
+        <v>10.33289458719768</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>16.94594712300419</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>10.38885420633975</v>
+        <v>8.9721922691116</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>15.58328130950962</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>12.30620747273377</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>8.425358797846126</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>10.23079282595601</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>3.362485887045325</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>48.92137437965848</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7.444556970817595</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.965099051003619</v>
+        <v>6.431429210520855</v>
       </c>
       <c r="C2" t="n">
-        <v>2.094067853158446</v>
+        <v>2.423935081785375</v>
       </c>
       <c r="D2" t="n">
-        <v>10.45463130252428</v>
+        <v>15.73250696055514</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.09838005906971</v>
+        <v>24.54860134469149</v>
       </c>
       <c r="C3" t="n">
-        <v>23.12506717353362</v>
+        <v>24.68113728476482</v>
       </c>
       <c r="D3" t="n">
-        <v>50.81526117181491</v>
+        <v>67.56387700626549</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.24466046700248</v>
+        <v>26.21462719879833</v>
       </c>
       <c r="C4" t="n">
-        <v>50.78286349757476</v>
+        <v>53.00357680458105</v>
       </c>
       <c r="D4" t="n">
-        <v>74.0110141800543</v>
+        <v>93.23167073379835</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.44738352016284</v>
+        <v>38.11635461738242</v>
       </c>
       <c r="C5" t="n">
-        <v>57.97220193577417</v>
+        <v>58.31581363226055</v>
       </c>
       <c r="D5" t="n">
-        <v>45.92124886614456</v>
+        <v>55.76326960121884</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.89189424600839</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>66.01271563355554</v>
+        <v>64.76491430145784</v>
       </c>
       <c r="D6" t="n">
-        <v>22.86294053649972</v>
+        <v>24.19124518034566</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>22.75691178444107</v>
       </c>
       <c r="C7" t="n">
-        <v>53.05953642372311</v>
+        <v>53.35896947351839</v>
       </c>
       <c r="D7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.4992929753009</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>33.71321616383547</v>
+        <v>35.04839304161113</v>
       </c>
       <c r="D8" t="n">
-        <v>19.27661617288612</v>
+        <v>20.02765316663493</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>20.41249826669968</v>
+        <v>21.29999819133879</v>
       </c>
       <c r="D9" t="n">
-        <v>20.63437324785945</v>
+        <v>19.52499834206056</v>
       </c>
     </row>
     <row r="10">
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
         <v>14.94710879715769</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>19.01350778814797</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6508987279156353</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>15.18763698469816</v>
+        <v>18.65909686691488</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>8.296749848589794</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="D14" t="n">
-        <v>10.44775906859456</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>7.525096153051802</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>14.33351648200343</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8.679631453246051</v>
+        <v>7.439684102782329</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>13.22610507161303</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>10.38885420633975</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>6.955682484588652</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>8.560839981032187</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>2.407245370813179</v>
+        <v>7.221736112439537</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>30.26237298340792</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.291800052339555</v>
+        <v>3.62559427178347</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9385508052599506</v>
+        <v>1.124101121362598</v>
       </c>
       <c r="D2" t="n">
-        <v>7.434775364261095</v>
+        <v>11.3568574427271</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.65168485363741</v>
+        <v>25.00511402716626</v>
       </c>
       <c r="C3" t="n">
-        <v>15.34471661737765</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="D3" t="n">
-        <v>48.22344723260333</v>
+        <v>65.099690268606</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.6147225982413</v>
+        <v>41.32568786256524</v>
       </c>
       <c r="C4" t="n">
-        <v>56.33464676509047</v>
+        <v>59.29559784109885</v>
       </c>
       <c r="D4" t="n">
-        <v>85.03800439415447</v>
+        <v>108.0109006735298</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.42975311921541</v>
+        <v>42.82874359776711</v>
       </c>
       <c r="C5" t="n">
-        <v>77.60715602071038</v>
+        <v>77.7544181763474</v>
       </c>
       <c r="D5" t="n">
-        <v>60.64746442984672</v>
+        <v>75.2755052231242</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.03531152628644</v>
+        <v>45.80638438474769</v>
       </c>
       <c r="C6" t="n">
-        <v>81.22784155397261</v>
+        <v>79.29576207201488</v>
       </c>
       <c r="D6" t="n">
-        <v>29.7057220351</v>
+        <v>33.61013265488955</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.78738702100172</v>
+        <v>30.66194429903638</v>
       </c>
       <c r="C7" t="n">
-        <v>70.60631314172635</v>
+        <v>70.66619975168541</v>
       </c>
       <c r="D7" t="n">
-        <v>23.29589127407256</v>
+        <v>23.53543771390878</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>45.89670517353839</v>
+        <v>46.89808783187013</v>
       </c>
       <c r="D8" t="n">
-        <v>20.11110172149591</v>
+        <v>22.19731559302038</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.549999698556465</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>21.1890607007589</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>15.9435827169682</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="D10" t="n">
-        <v>20.4988920646734</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>13.68261775408779</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="D11" t="n">
-        <v>18.30272245027328</v>
+        <v>20.25738212942868</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>8.027750977626168</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>14.97067074205961</v>
+        <v>19.30999559483051</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>6.764241682260525</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>17.69109363052753</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>6.145740628585034</v>
+        <v>7.067601722872788</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.091744504851459</v>
       </c>
       <c r="D15" t="n">
-        <v>2.866703296400686</v>
+        <v>11.10847527355266</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8.679631453246051</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>7.083309686140737</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605157496443535</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>4.280419990516093</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>26.47969907894496</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.904811530417065</v>
+        <v>5.046183199828605</v>
       </c>
       <c r="C2" t="n">
-        <v>3.938771789438203</v>
+        <v>4.177336481570178</v>
       </c>
       <c r="D2" t="n">
-        <v>5.500732386894879</v>
+        <v>8.515679586636832</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.4050041379642</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C3" t="n">
-        <v>8.874999246391166</v>
+        <v>10.20526738564559</v>
       </c>
       <c r="D3" t="n">
-        <v>43.11345043199868</v>
+        <v>58.90977099332986</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.46830332158828</v>
+        <v>48.37070938824035</v>
       </c>
       <c r="C4" t="n">
-        <v>47.17101369365075</v>
+        <v>50.50208365416017</v>
       </c>
       <c r="D4" t="n">
-        <v>91.39383903144832</v>
+        <v>117.0724319837279</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.7758523949248</v>
+        <v>56.79410469067799</v>
       </c>
       <c r="C5" t="n">
-        <v>91.76886665447061</v>
+        <v>93.53601252211487</v>
       </c>
       <c r="D5" t="n">
-        <v>78.14711725804612</v>
+        <v>98.3956636581366</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.82275530055039</v>
+        <v>56.19131160027045</v>
       </c>
       <c r="C6" t="n">
-        <v>103.2052456612417</v>
+        <v>100.7096429970463</v>
       </c>
       <c r="D6" t="n">
-        <v>40.97618567985338</v>
+        <v>49.50953672516665</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.59745205019235</v>
+        <v>46.77144237802229</v>
       </c>
       <c r="C7" t="n">
-        <v>93.60277136600364</v>
+        <v>92.64458560665875</v>
       </c>
       <c r="D7" t="n">
-        <v>26.52976821186155</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.44489594093983</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="C8" t="n">
-        <v>67.34298377280996</v>
+        <v>68.59471209572465</v>
       </c>
       <c r="D8" t="n">
-        <v>21.69662426385451</v>
+        <v>23.699389580518</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>8.653124265231384</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.63281066307846</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.850594422505238</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>20.21418523044183</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
         <v>21.21065915025234</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>1.066178006812036</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>18.65811511921063</v>
+        <v>20.96816746730337</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>9.76348091873453</v>
+        <v>12.58404207303562</v>
       </c>
       <c r="D12" t="n">
-        <v>14.53673825678252</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>7.544731107136739</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>18.21141991377833</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>6.760314691443536</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>12.59876828859932</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>7.883434065101886</v>
+        <v>6.450082416901544</v>
       </c>
       <c r="D15" t="n">
-        <v>1.791689560250429</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>7.852999886270235</v>
+        <v>5.7864209688307</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>3.777765165941727</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>6.611089040398022</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>13.37631247036279</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>3.745367491701582</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>15.04528356758237</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.267837196810132</v>
+        <v>2.471058971589222</v>
       </c>
       <c r="C2" t="n">
-        <v>1.675843331149305</v>
+        <v>1.877101610519901</v>
       </c>
       <c r="D2" t="n">
-        <v>3.640320487347172</v>
+        <v>5.704935909378215</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.17353266394021</v>
+        <v>19.49260066782042</v>
       </c>
       <c r="C3" t="n">
-        <v>12.68418033886879</v>
+        <v>13.62174939642449</v>
       </c>
       <c r="D3" t="n">
-        <v>39.96694903988765</v>
+        <v>54.98768891486385</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.17850782238623</v>
+        <v>50.24682925105601</v>
       </c>
       <c r="C4" t="n">
-        <v>42.37223091529233</v>
+        <v>46.00960615952677</v>
       </c>
       <c r="D4" t="n">
-        <v>96.46063893306611</v>
+        <v>123.6324701435051</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.03573779910973</v>
+        <v>70.36676670189014</v>
       </c>
       <c r="C5" t="n">
-        <v>106.1514705216864</v>
+        <v>106.7896065294468</v>
       </c>
       <c r="D5" t="n">
-        <v>87.5718952188155</v>
+        <v>111.6492576654685</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.54099370943156</v>
+        <v>57.19760299712343</v>
       </c>
       <c r="C6" t="n">
-        <v>126.9134709710979</v>
+        <v>125.7864246066226</v>
       </c>
       <c r="D6" t="n">
-        <v>40.49316580936395</v>
+        <v>48.94601354292898</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>95.99823576436586</v>
+        <v>95.33948305481626</v>
       </c>
       <c r="D7" t="n">
-        <v>26.4698816019025</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>45.89670517353839</v>
+        <v>52.82293522699963</v>
       </c>
       <c r="D8" t="n">
-        <v>23.61594102565702</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.331249886958674</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>15.42031119060464</v>
+        <v>16.86249856814321</v>
       </c>
       <c r="D9" t="n">
-        <v>21.52187317249857</v>
+        <v>23.2968730217768</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1423534171157875</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>12.38474728907351</v>
+        <v>12.81180754042088</v>
       </c>
       <c r="D10" t="n">
-        <v>14.52004854581033</v>
+        <v>16.37064296831556</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>7.818638716621595</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="D11" t="n">
-        <v>11.55026174046372</v>
+        <v>15.81497376771187</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>6.075054793879263</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="D12" t="n">
-        <v>7.376852249710534</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>5.463425974133501</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="D13" t="n">
-        <v>4.162610266006476</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>6.453027660014286</v>
+        <v>5.223879534297279</v>
       </c>
       <c r="D14" t="n">
-        <v>1.229148125717007</v>
+        <v>9.525897974306801</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>6.450082416901544</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2.89321048441535</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5.373105185342793</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>11.33329549782518</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2.833323874456295</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.087416603406972</v>
+        <v>4.994150571503524</v>
       </c>
       <c r="C2" t="n">
-        <v>1.875138115111408</v>
+        <v>2.042035224833366</v>
       </c>
       <c r="D2" t="n">
-        <v>4.477751279069702</v>
+        <v>7.016550842251953</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.39456476611598</v>
+        <v>13.03760951239764</v>
       </c>
       <c r="C3" t="n">
-        <v>9.464047868939252</v>
+        <v>10.36725575684632</v>
       </c>
       <c r="D3" t="n">
-        <v>33.75248607200535</v>
+        <v>47.02080629490099</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.11621574866217</v>
+        <v>44.29940165872883</v>
       </c>
       <c r="C4" t="n">
-        <v>37.20332925243288</v>
+        <v>39.96007680595792</v>
       </c>
       <c r="D4" t="n">
-        <v>95.87355380592652</v>
+        <v>123.5814192628842</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79.71791358484101</v>
+        <v>77.43535017246718</v>
       </c>
       <c r="C5" t="n">
-        <v>94.37049807072466</v>
+        <v>97.14393533522191</v>
       </c>
       <c r="D5" t="n">
-        <v>102.6662661716102</v>
+        <v>131.2351243651924</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>81.02658327460202</v>
+        <v>80.74482168348318</v>
       </c>
       <c r="C6" t="n">
-        <v>149.8166631634718</v>
+        <v>147.1198022199058</v>
       </c>
       <c r="D6" t="n">
-        <v>56.55357650313753</v>
+        <v>71.92970904705108</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.96244121199391</v>
+        <v>46.77144237802229</v>
       </c>
       <c r="C7" t="n">
-        <v>135.1640786775881</v>
+        <v>134.9245322377519</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>77.35681035612741</v>
+        <v>83.11476064153496</v>
       </c>
       <c r="D8" t="n">
-        <v>25.36836067773758</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>3.771874679716245</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>22.63124807829746</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>14.66240196292611</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="D10" t="n">
-        <v>15.08946221427348</v>
+        <v>17.93653055658923</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>9.417905726839649</v>
+        <v>11.72795807493239</v>
       </c>
       <c r="D11" t="n">
-        <v>11.19486907152638</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>6.942919764433443</v>
+        <v>8.461683462903258</v>
       </c>
       <c r="D12" t="n">
-        <v>6.942919764433443</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>5.983752257384309</v>
+        <v>7.284567965511334</v>
       </c>
       <c r="D13" t="n">
-        <v>3.382120841130262</v>
+        <v>10.6666888066416</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>6.760314691443536</v>
+        <v>5.53116656572653</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6145740628585034</v>
+        <v>9.21861094287755</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>4.546473618366978</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1.888882582970863</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.654064955206628</v>
+        <v>3.62264902867073</v>
       </c>
       <c r="C2" t="n">
-        <v>1.005309649148734</v>
+        <v>1.128028112179585</v>
       </c>
       <c r="D2" t="n">
-        <v>3.629521262600458</v>
+        <v>5.688246198406019</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.57680998620739</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C3" t="n">
-        <v>8.580474935117122</v>
+        <v>9.326603190344699</v>
       </c>
       <c r="D3" t="n">
-        <v>30.29673415305657</v>
+        <v>42.79438242811847</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.51414236405162</v>
+        <v>36.59071868498287</v>
       </c>
       <c r="C4" t="n">
-        <v>32.28968199267759</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D4" t="n">
-        <v>93.47416241674732</v>
+        <v>120.7863835488936</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>82.58952561976294</v>
+        <v>79.10432126968676</v>
       </c>
       <c r="C5" t="n">
-        <v>87.25282721493528</v>
+        <v>90.32078879070657</v>
       </c>
       <c r="D5" t="n">
-        <v>113.4654909183251</v>
+        <v>145.0777669950724</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>98.93857013858508</v>
+        <v>96.6844774096344</v>
       </c>
       <c r="C6" t="n">
-        <v>160.6041069377357</v>
+        <v>157.2229678443097</v>
       </c>
       <c r="D6" t="n">
-        <v>68.2265567066321</v>
+        <v>88.91590782592939</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.47874269343649</v>
+        <v>61.56343503790898</v>
       </c>
       <c r="C7" t="n">
-        <v>167.1435283957237</v>
+        <v>166.3051158562969</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>41.9206269713388</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>103.6431051373358</v>
+        <v>109.4010554227433</v>
       </c>
       <c r="D8" t="n">
-        <v>25.95250056176443</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.331249886958674</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>31.61718481526852</v>
+        <v>44.04218376021615</v>
       </c>
       <c r="D9" t="n">
-        <v>21.74374815365835</v>
+        <v>24.29531043699581</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>14.23534171157875</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="D10" t="n">
-        <v>14.52004854581033</v>
+        <v>18.36359080793659</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>9.062513057902304</v>
+        <v>11.37256540599505</v>
       </c>
       <c r="D11" t="n">
-        <v>9.773298395776996</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>5.858088551240717</v>
+        <v>8.244717220264713</v>
       </c>
       <c r="D12" t="n">
-        <v>4.990223580686536</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="D13" t="n">
-        <v>1.040652566501619</v>
+        <v>10.6666888066416</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>3.994731408580272</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>7.067601722872788</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3583379120500857</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3.583379120500858</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1.239947350463722</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.40532293313369</v>
+        <v>6.990043654237289</v>
       </c>
       <c r="C2" t="n">
-        <v>2.752820562708056</v>
+        <v>2.882411259668635</v>
       </c>
       <c r="D2" t="n">
-        <v>4.008475876439727</v>
+        <v>6.333254440096174</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.67712817848982</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="C3" t="n">
-        <v>6.253732876052182</v>
+        <v>6.906595099376311</v>
       </c>
       <c r="D3" t="n">
-        <v>26.75262494072558</v>
+        <v>38.00836236991526</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.37826027023806</v>
+        <v>34.33171721751096</v>
       </c>
       <c r="C4" t="n">
-        <v>27.32498385230147</v>
+        <v>29.40530723760046</v>
       </c>
       <c r="D4" t="n">
-        <v>88.0882945112493</v>
+        <v>114.3029217100476</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.10307748007526</v>
+        <v>68.69779560467057</v>
       </c>
       <c r="C5" t="n">
-        <v>75.39822368615505</v>
+        <v>78.53981633974485</v>
       </c>
       <c r="D5" t="n">
-        <v>121.9085211748477</v>
+        <v>155.7297295861503</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>111.4970867713103</v>
+        <v>106.344874819423</v>
       </c>
       <c r="C6" t="n">
-        <v>153.6808221273872</v>
+        <v>152.1512592041707</v>
       </c>
       <c r="D6" t="n">
-        <v>84.93099389439158</v>
+        <v>112.0203582976738</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87.85365680993432</v>
+        <v>92.58469899669969</v>
       </c>
       <c r="C7" t="n">
-        <v>197.745586084801</v>
+        <v>192.7151108482404</v>
       </c>
       <c r="D7" t="n">
-        <v>44.85507085933252</v>
+        <v>55.63466065196249</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.45733986592554</v>
+        <v>39.30426933952106</v>
       </c>
       <c r="C8" t="n">
-        <v>149.957053085179</v>
+        <v>154.8805178219768</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.771874679716245</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>64.78749449865549</v>
+        <v>80.20780568926014</v>
       </c>
       <c r="D9" t="n">
-        <v>22.74218556887735</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>15.51652246562084</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>11.19486907152638</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="D11" t="n">
-        <v>9.417905726839649</v>
+        <v>17.05884810899257</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>6.725953521794898</v>
+        <v>9.76348091873453</v>
       </c>
       <c r="D12" t="n">
-        <v>4.556291095409447</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>5.983752257384309</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7804894248762143</v>
+        <v>10.926851948267</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3.68744437715102</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>7.37488875430204</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>6.808420328951629</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3.583379120500858</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.8266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.920118583057514</v>
+        <v>3.932881303212722</v>
       </c>
       <c r="C2" t="n">
-        <v>8.346818981506383</v>
+        <v>8.490154146326416</v>
       </c>
       <c r="D2" t="n">
-        <v>2.645810062945154</v>
+        <v>3.184789552576653</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06381360077604269</v>
+        <v>0.05890486225480862</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.201880174176348</v>
+        <v>4.157701527485242</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.182425146540659</v>
+        <v>2.067560665143783</v>
       </c>
       <c r="C4" t="n">
-        <v>4.87535909928966</v>
+        <v>4.722206457427157</v>
       </c>
       <c r="D4" t="n">
-        <v>23.72589676853267</v>
+        <v>23.31748972356599</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.528622233241291</v>
+        <v>6.45499115542278</v>
       </c>
       <c r="C5" t="n">
-        <v>12.56637061435918</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D5" t="n">
-        <v>25.52544031041707</v>
+        <v>25.89359569950963</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.808821239579131</v>
+        <v>7.889324551327369</v>
       </c>
       <c r="C6" t="n">
-        <v>16.22141731727005</v>
+        <v>16.1006623496477</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4428346345401</v>
+        <v>31.87931145230244</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>17.48689010804419</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>29.58398531977338</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>19.10971906316416</v>
+        <v>18.85937339858123</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3991,7 +3991,7 @@
         <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>21.07812321017901</v>
+        <v>21.1890607007589</v>
       </c>
       <c r="D9" t="n">
         <v>39.160934174701</v>
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>54.6637121724624</v>
+        <v>53.09782458418874</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.219371706403542</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
-        <v>42.82481660695011</v>
+        <v>44.06869094823081</v>
       </c>
     </row>
     <row r="12">
@@ -4033,10 +4033,10 @@
         <v>5.424156065963627</v>
       </c>
       <c r="C12" t="n">
-        <v>22.99842171968578</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>43.39324852770902</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -4044,10 +4044,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4061,10 +4061,10 @@
         <v>5.223879534297279</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>44.24933252581224</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.091744504851459</v>
+        <v>5.733406592801372</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>42.64221153396021</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.613052535806514</v>
+        <v>6.199736752318607</v>
       </c>
       <c r="C16" t="n">
-        <v>30.99868376159304</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>39.26499943135118</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -4103,10 +4103,10 @@
         <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>34.47210713921825</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -4117,10 +4117,10 @@
         <v>7.490734983403163</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>28.35778243716912</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -4131,10 +4131,10 @@
         <v>7.823547455142832</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>19.25796296650543</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -4145,10 +4145,10 @@
         <v>8.06996612890878</v>
       </c>
       <c r="C20" t="n">
-        <v>46.40230524122548</v>
+        <v>40.34983064454389</v>
       </c>
       <c r="D20" t="n">
-        <v>8.06996612890878</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>4.330673360958459</v>
+        <v>10.72628908181822</v>
       </c>
       <c r="C21" t="n">
-        <v>24.5404823787646</v>
+        <v>53.6314454090911</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.7661635058441586</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.203843669584842</v>
+        <v>4.188135706316893</v>
       </c>
       <c r="C2" t="n">
-        <v>1.452986602285279</v>
+        <v>1.590431280879833</v>
       </c>
       <c r="D2" t="n">
-        <v>2.821542902005333</v>
+        <v>4.5091672056056</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.82210804354885</v>
+        <v>21.95678740547991</v>
       </c>
       <c r="C3" t="n">
-        <v>8.845546815263761</v>
+        <v>9.341329405908402</v>
       </c>
       <c r="D3" t="n">
-        <v>28.39214360681776</v>
+        <v>39.80986940720816</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.16123727433728</v>
+        <v>49.87671036655495</v>
       </c>
       <c r="C4" t="n">
-        <v>39.48785616021521</v>
+        <v>42.23184099358505</v>
       </c>
       <c r="D4" t="n">
-        <v>96.51168981368694</v>
+        <v>124.6534877559218</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.97468951499718</v>
+        <v>71.32397071353078</v>
       </c>
       <c r="C5" t="n">
-        <v>123.9211039685537</v>
+        <v>122.7675504160637</v>
       </c>
       <c r="D5" t="n">
-        <v>115.4780737120311</v>
+        <v>149.5447190493954</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.54099370943156</v>
+        <v>57.47936458824226</v>
       </c>
       <c r="C6" t="n">
-        <v>161.8519082698334</v>
+        <v>161.2078817758475</v>
       </c>
       <c r="D6" t="n">
-        <v>67.58253021264619</v>
+        <v>88.59389457893643</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>26.05067533218911</v>
       </c>
       <c r="C7" t="n">
-        <v>105.4603201378966</v>
+        <v>108.8738569055628</v>
       </c>
       <c r="D7" t="n">
-        <v>25.33203601268044</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.586905200690345</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>47.73257338047992</v>
+        <v>59.08157684157305</v>
       </c>
       <c r="D8" t="n">
-        <v>16.68971097219578</v>
+        <v>19.19316761802514</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1109374905798895</v>
+        <v>0.8874999246391163</v>
       </c>
       <c r="C9" t="n">
-        <v>16.30781111524376</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>11.75937400146829</v>
+        <v>15.19843620944487</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8.683558444063038</v>
+        <v>10.96121311791564</v>
       </c>
       <c r="D10" t="n">
-        <v>7.260024272905163</v>
+        <v>13.38122120888403</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5.330890034060179</v>
+        <v>7.818638716621595</v>
       </c>
       <c r="D11" t="n">
-        <v>3.553926689373453</v>
+        <v>11.55026174046372</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>4.773257338047991</v>
+        <v>4.556291095409447</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4339324852770902</v>
+        <v>8.895615948180348</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>5.983752257384309</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>5.53116656572653</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.17381040138069</v>
+        <v>5.331871781764427</v>
       </c>
       <c r="C2" t="n">
-        <v>5.790347959647687</v>
+        <v>5.979825266567322</v>
       </c>
       <c r="D2" t="n">
-        <v>9.351146882950868</v>
+        <v>11.86540275352695</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.586766331970104</v>
+        <v>9.611310024576275</v>
       </c>
       <c r="C3" t="n">
-        <v>17.69109363052752</v>
+        <v>17.99543541884404</v>
       </c>
       <c r="D3" t="n">
-        <v>5.448699758569798</v>
+        <v>5.82667262470482</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.880627690709389</v>
+        <v>0.7912886496229291</v>
       </c>
       <c r="C4" t="n">
-        <v>2.335577788403162</v>
+        <v>2.220713307006285</v>
       </c>
       <c r="D4" t="n">
-        <v>20.53521672973053</v>
+        <v>19.85879256150448</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.810563750809371</v>
+        <v>4.491495746929158</v>
       </c>
       <c r="C5" t="n">
-        <v>10.87285582453343</v>
+        <v>10.45561305022853</v>
       </c>
       <c r="D5" t="n">
-        <v>28.6424892714007</v>
+        <v>28.91246989006857</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.93586760405447</v>
+        <v>8.855364292306232</v>
       </c>
       <c r="C6" t="n">
-        <v>18.03274183160542</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="D6" t="n">
-        <v>33.85164259013428</v>
+        <v>33.12711278440013</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>20.54110721595601</v>
+        <v>20.60099382591507</v>
       </c>
       <c r="D7" t="n">
-        <v>32.27888276793088</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>21.44627859927157</v>
+        <v>21.19593293468863</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>9.762499171030278</v>
       </c>
       <c r="C9" t="n">
-        <v>22.85312305945724</v>
+        <v>22.63124807829746</v>
       </c>
       <c r="D9" t="n">
-        <v>40.49218406165969</v>
+        <v>40.38124657107979</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>54.23665192111504</v>
+        <v>51.53193699591508</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.107853378746905</v>
+        <v>7.818638716621595</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>44.60177995163684</v>
+        <v>47.44492130313559</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>45.12897846881738</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.48789721794422</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>44.24933252581224</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
-        <v>41.56719779780995</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.613052535806514</v>
+        <v>5.7864209688307</v>
       </c>
       <c r="C16" t="n">
-        <v>31.82531532856885</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>38.02505208088746</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>6.138868394655306</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>33.0554452019901</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -4739,10 +4739,10 @@
         <v>6.955682484588652</v>
       </c>
       <c r="C18" t="n">
-        <v>36.38356991938679</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>25.68251994309656</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -4753,10 +4753,10 @@
         <v>7.221736112439537</v>
       </c>
       <c r="C19" t="n">
-        <v>38.51592593301086</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8.742463306317845</v>
+        <v>7.397468951499714</v>
       </c>
       <c r="C20" t="n">
-        <v>61.86974032163398</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
-        <v>4.707480241863455</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>12.72425335851654</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>68.3928618020264</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.385797504721851</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.376230354904781</v>
+        <v>3.718860303686918</v>
       </c>
       <c r="C2" t="n">
-        <v>3.910301106015046</v>
+        <v>4.141011816513046</v>
       </c>
       <c r="D2" t="n">
-        <v>9.044841599225864</v>
+        <v>11.59640388256332</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.76195939168254</v>
+        <v>15.93867397844697</v>
       </c>
       <c r="C3" t="n">
-        <v>20.36144738607885</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="D3" t="n">
-        <v>12.03622685406589</v>
+        <v>14.38260386721577</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.85205919629499</v>
+        <v>12.83929647613979</v>
       </c>
       <c r="C4" t="n">
-        <v>23.66208316775662</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D4" t="n">
-        <v>18.68462230722529</v>
+        <v>18.30174070256904</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.896155727528091</v>
+        <v>2.552544031041708</v>
       </c>
       <c r="C5" t="n">
-        <v>7.633088400518952</v>
+        <v>7.264933011426399</v>
       </c>
       <c r="D5" t="n">
-        <v>30.01693605734623</v>
+        <v>29.52606220522283</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.969827863075609</v>
+        <v>7.567311304334416</v>
       </c>
       <c r="C6" t="n">
-        <v>17.91198686398306</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="D6" t="n">
-        <v>35.86422538384024</v>
+        <v>35.38120551335081</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.77958979262998</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>23.41566449399068</v>
+        <v>23.17611805415445</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>24.45042657426681</v>
+        <v>24.28352946454485</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>10.42812411450962</v>
       </c>
       <c r="C9" t="n">
-        <v>25.07187287105504</v>
+        <v>24.96093538047515</v>
       </c>
       <c r="D9" t="n">
-        <v>41.71249645803847</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.680032363873552</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>54.52135875534661</v>
+        <v>50.96252332745193</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.996335051090269</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
         <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>46.02335062738621</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.99684343937156</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>44.48789721794422</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>43.63475846295374</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>28.30869505195678</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
-        <v>40.85052197370977</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.613052535806514</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>32.23863111205676</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>36.78510473042374</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>31.63878326476196</v>
+        <v>38.24987230515998</v>
       </c>
     </row>
     <row r="18">
@@ -5050,10 +5050,10 @@
         <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>37.98872741583033</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>23.007257449024</v>
+        <v>33.17325492649972</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
-        <v>42.12679398923063</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>12.03622685406589</v>
+        <v>25.87788773624167</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>52.45477983790707</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
-        <v>2.68998870963626</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>14.83779708036817</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>83.25652806206583</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4.121610300102269</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.338343105066655</v>
+        <v>4.904811530417065</v>
       </c>
       <c r="C2" t="n">
-        <v>6.150649367106268</v>
+        <v>6.652322443976388</v>
       </c>
       <c r="D2" t="n">
-        <v>14.83224431576081</v>
+        <v>19.45823949817178</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.60702318086079</v>
+        <v>14.31388152791849</v>
       </c>
       <c r="C3" t="n">
-        <v>17.74999849278233</v>
+        <v>18.23105486786327</v>
       </c>
       <c r="D3" t="n">
-        <v>16.47863521578271</v>
+        <v>20.32217747790898</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.16808414607123</v>
+        <v>24.93835518327748</v>
       </c>
       <c r="C4" t="n">
-        <v>37.21609197258809</v>
+        <v>37.2288546927433</v>
       </c>
       <c r="D4" t="n">
-        <v>20.71389481190345</v>
+        <v>21.40308170028471</v>
       </c>
     </row>
     <row r="5">
@@ -5182,7 +5182,7 @@
         <v>24.91184799526282</v>
       </c>
       <c r="D5" t="n">
-        <v>30.40963513904496</v>
+        <v>29.37880004958581</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6.037748381117884</v>
+        <v>5.353470231257858</v>
       </c>
       <c r="C6" t="n">
-        <v>15.49688751153591</v>
+        <v>14.4503444588088</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>37.23278168356029</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>10.36038352291659</v>
       </c>
       <c r="C7" t="n">
-        <v>24.97271635292611</v>
+        <v>24.19419042345839</v>
       </c>
       <c r="D7" t="n">
-        <v>37.60879105428681</v>
+        <v>37.72856427420492</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.01659189998096</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>27.87181732356695</v>
+        <v>27.45457454926205</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.42656152972862</v>
+        <v>11.53749902030851</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>42.48905889209769</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.53415286656828</v>
+        <v>10.81885970079985</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>54.94841900669398</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>47.44492130313559</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5274,10 +5274,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>8.027750977626168</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
         <v>47.73257338047992</v>
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>6.50407854063512</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
       <c r="C14" t="n">
         <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>43.32747143152449</v>
+        <v>46.400341745817</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>39.77550823755952</v>
+        <v>44.43390109421063</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.613052535806514</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>33.06526267903257</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>35.95847316344792</v>
+        <v>42.15820991576653</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>37.30543101367455</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>29.27768003604838</v>
+        <v>38.24987230515998</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>39.05883241345935</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>19.79694245613693</v>
+        <v>33.70830742531424</v>
       </c>
     </row>
     <row r="19">
@@ -5375,10 +5375,10 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>43.93222801734051</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>26.47969907894496</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3.362485887045325</v>
+        <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>44.38481370899829</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
-        <v>1.34499435481813</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>16.20941128505199</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>97.25646771031194</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5.97188836817705</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.400594121061704</v>
+        <v>6.134941403838318</v>
       </c>
       <c r="C2" t="n">
-        <v>4.566108572451915</v>
+        <v>5.094288837336698</v>
       </c>
       <c r="D2" t="n">
-        <v>13.51572064436584</v>
+        <v>18.05826727191583</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.16309329209199</v>
+        <v>16.27737693641212</v>
       </c>
       <c r="C3" t="n">
-        <v>20.98976591679681</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D3" t="n">
-        <v>24.67622854624358</v>
+        <v>30.58634972580938</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.73789872516188</v>
+        <v>27.41432289338793</v>
       </c>
       <c r="C4" t="n">
-        <v>40.63650097418398</v>
+        <v>40.6747891346496</v>
       </c>
       <c r="D4" t="n">
-        <v>24.10877837318892</v>
+        <v>26.27844079957437</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.20070280448963</v>
+        <v>27.34167356327368</v>
       </c>
       <c r="C5" t="n">
-        <v>45.67581194008286</v>
+        <v>44.76769531365456</v>
       </c>
       <c r="D5" t="n">
-        <v>31.39138284329177</v>
+        <v>30.63052837250049</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.67927160034756</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="C6" t="n">
-        <v>26.04282135055514</v>
+        <v>25.55980148006571</v>
       </c>
       <c r="D6" t="n">
-        <v>39.20511282139213</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>22.99645822427728</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>40.42346172236242</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="C8" t="n">
-        <v>30.70906818884022</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D8" t="n">
-        <v>41.0566889916016</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>12.7578114166873</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39530983410874</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>43.82030877905637</v>
+        <v>42.93280885441725</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11.388273369263</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>54.8060655895782</v>
+        <v>49.96604940764142</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.773298395776996</v>
+        <v>10.66178006812036</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>49.22188464782232</v>
+        <v>52.24272233378976</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>8.895615948180348</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
         <v>48.81740459367264</v>
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>7.284567965511334</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
-        <v>43.96757093469341</v>
+        <v>46.82936549257286</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.53116656572653</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>43.02018440009523</v>
+        <v>46.400341745817</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
       <c r="D15" t="n">
-        <v>39.05883241345935</v>
+        <v>45.15057691831081</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>33.89189424600838</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>34.7185258129842</v>
+        <v>42.15820991576653</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>39.66653424238813</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>26.9165768073348</v>
+        <v>38.72209295090269</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>40.12893741108837</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>17.12167996206437</v>
+        <v>33.70830742531424</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.814490741626358</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>44.53403936004381</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>6.619924769736241</v>
+        <v>27.08151042164826</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.017491532227195</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>36.98734475749858</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
-        <v>0.672497177409065</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>17.62701249438532</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>111.9315293393468</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7.932155622473392</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.095270585040946</v>
+        <v>5.802128932098649</v>
       </c>
       <c r="C2" t="n">
-        <v>4.813508993922111</v>
+        <v>5.39568538254047</v>
       </c>
       <c r="D2" t="n">
-        <v>15.44878187402781</v>
+        <v>21.01823660021996</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.9583089325319</v>
+        <v>17.11677122354314</v>
       </c>
       <c r="C3" t="n">
-        <v>17.51928778228433</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D3" t="n">
-        <v>27.56747553525044</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.78221624057323</v>
+        <v>20.53521672973053</v>
       </c>
       <c r="C4" t="n">
-        <v>36.46309148343079</v>
+        <v>36.6290068454485</v>
       </c>
       <c r="D4" t="n">
-        <v>25.74240655305561</v>
+        <v>29.34149363682442</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.32217747790898</v>
+        <v>20.17491532227196</v>
       </c>
       <c r="C5" t="n">
-        <v>41.30703465618456</v>
+        <v>40.44800541496859</v>
       </c>
       <c r="D5" t="n">
-        <v>25.86905200690346</v>
+        <v>25.89359569950963</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.20883452356409</v>
+        <v>13.64531134132642</v>
       </c>
       <c r="C6" t="n">
-        <v>30.06798693796707</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D6" t="n">
-        <v>30.02773528209295</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>18.26541603751191</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>17.7745421853885</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>19.52499834206056</v>
+        <v>18.97031088916111</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.50594422505238</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>18.65811511921063</v>
+        <v>18.12502611580461</v>
       </c>
       <c r="D11" t="n">
-        <v>33.22921454564179</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
         <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>28.09761929554372</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>26.73397173434489</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>24.00864010735575</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.066578917439536</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>20.77770841267949</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>15.11106066376691</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5983,10 +5983,10 @@
         <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>19.79694245613693</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>8.560839981032187</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>21.06339699461531</v>
+        <v>17.45252893839555</v>
       </c>
       <c r="D19" t="n">
-        <v>2.407245370813179</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>14.79493790299943</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5.452959181548228</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>60.89137752728854</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5.452959181548228</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.950552761889165</v>
+        <v>4.420809912223387</v>
       </c>
       <c r="C2" t="n">
-        <v>3.133738671955819</v>
+        <v>3.584360868205105</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35239067256238</v>
+        <v>24.13823080431633</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.57190124768616</v>
+        <v>18.07888397370501</v>
       </c>
       <c r="C3" t="n">
-        <v>16.94496537529995</v>
+        <v>18.30468594568178</v>
       </c>
       <c r="D3" t="n">
-        <v>32.53511891873929</v>
+        <v>41.37084825696059</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.72665753205866</v>
+        <v>21.8242514654066</v>
       </c>
       <c r="C4" t="n">
-        <v>32.80019079888594</v>
+        <v>33.36175048571511</v>
       </c>
       <c r="D4" t="n">
-        <v>29.64779892054943</v>
+        <v>35.04642954620264</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.78159434576748</v>
+        <v>16.00248757922301</v>
       </c>
       <c r="C5" t="n">
-        <v>39.24536447726625</v>
+        <v>39.1226460142354</v>
       </c>
       <c r="D5" t="n">
-        <v>23.63557597974196</v>
+        <v>24.86276061005048</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>31.79880814055419</v>
+        <v>30.71201343195298</v>
       </c>
       <c r="D6" t="n">
-        <v>23.90948358922682</v>
+        <v>23.18495378349268</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>19.16371518689774</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="D7" t="n">
-        <v>23.65521093382689</v>
+        <v>23.59532432386784</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.837250865273282</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>12.76762889372977</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="D8" t="n">
         <v>21.86352137357647</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>12.31406145436774</v>
+        <v>11.75937400146829</v>
       </c>
       <c r="D9" t="n">
-        <v>21.41093568191868</v>
+        <v>21.1890607007589</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>11.81533362061037</v>
+        <v>11.388273369263</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>11.0171727370577</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="D11" t="n">
-        <v>22.38973814305275</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>1.518763698469816</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7804894248762143</v>
+        <v>1.040652566501619</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>17.95125677215293</v>
+        <v>20.03256190515617</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>8.296749848589794</v>
+        <v>8.911323911448299</v>
       </c>
       <c r="D14" t="n">
-        <v>16.90078672860884</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>14.69185439405351</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>8.679631453246051</v>
+        <v>7.852999886270235</v>
       </c>
       <c r="D16" t="n">
-        <v>11.98615772114931</v>
+        <v>16.94594712300419</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>10.38885420633975</v>
+        <v>7.555530331883453</v>
       </c>
       <c r="D17" t="n">
-        <v>8.499971623368884</v>
+        <v>15.11106066376691</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>10.16599747747572</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>4.280419990516093</v>
+        <v>12.84125997154828</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>9.628981483252716</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6018113427032947</v>
+        <v>10.23079282595601</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>6.052474596681584</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1.88798396894705</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>33.03971945657337</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.7759679378941</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.161227607674729</v>
+        <v>3.500912313344126</v>
       </c>
       <c r="C2" t="n">
-        <v>1.824087234490574</v>
+        <v>2.076396394482004</v>
       </c>
       <c r="D2" t="n">
-        <v>15.16309329209199</v>
+        <v>21.32650537935346</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.48707003449343</v>
+        <v>17.01859645311846</v>
       </c>
       <c r="C3" t="n">
-        <v>13.9113649691773</v>
+        <v>15.59506228196058</v>
       </c>
       <c r="D3" t="n">
-        <v>41.08614142272901</v>
+        <v>53.92249265575606</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.89403766786613</v>
+        <v>34.19132729580366</v>
       </c>
       <c r="C4" t="n">
-        <v>39.23260175711104</v>
+        <v>40.6747891346496</v>
       </c>
       <c r="D4" t="n">
-        <v>41.40226418349649</v>
+        <v>51.38271134486956</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.37250865273283</v>
+        <v>29.550605897829</v>
       </c>
       <c r="C5" t="n">
-        <v>52.52350217720437</v>
+        <v>52.71985171805373</v>
       </c>
       <c r="D5" t="n">
-        <v>30.50780990946964</v>
+        <v>33.64940256305943</v>
       </c>
     </row>
     <row r="6">
@@ -6437,10 +6437,10 @@
         <v>20.12582793705961</v>
       </c>
       <c r="C6" t="n">
-        <v>49.22777513404782</v>
+        <v>48.66425195181016</v>
       </c>
       <c r="D6" t="n">
-        <v>26.76735115628929</v>
+        <v>26.88810612391165</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.99539436111503</v>
+        <v>13.29482741091031</v>
       </c>
       <c r="C7" t="n">
-        <v>34.49468733641593</v>
+        <v>33.71616140694821</v>
       </c>
       <c r="D7" t="n">
         <v>25.81112889235289</v>
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>20.11110172149591</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D8" t="n">
-        <v>23.699389580518</v>
+        <v>23.78283813537898</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>14.53281126596553</v>
+        <v>14.08906130364597</v>
       </c>
       <c r="D9" t="n">
         <v>22.63124807829746</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>13.6659280431156</v>
+        <v>13.09651437465245</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>2.132356013624072</v>
       </c>
       <c r="C11" t="n">
-        <v>12.61643974727576</v>
+        <v>12.43874341280708</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.301797455831271</v>
+        <v>1.735729941108361</v>
       </c>
       <c r="C12" t="n">
         <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.78145547704723</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7804894248762143</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>10.40652566501619</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.55288818840698</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>9.21861094287755</v>
+        <v>10.14047203716531</v>
       </c>
       <c r="D14" t="n">
-        <v>16.90078672860884</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>8.241771977151972</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>14.33351648200343</v>
+        <v>18.63357142660446</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8.679631453246051</v>
+        <v>8.266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>11.15952615417349</v>
+        <v>16.94594712300419</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>10.38885420633975</v>
+        <v>8.02775097762617</v>
       </c>
       <c r="D17" t="n">
-        <v>7.555530331883453</v>
+        <v>15.58328130950962</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>10.70104997629023</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>9.628981483252716</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>10.23079282595601</v>
       </c>
     </row>
     <row r="20">
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>5.37997741927252</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.9846301378820086</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>37.41594523951633</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4.923150689410043</v>
       </c>
     </row>
   </sheetData>
